--- a/InputData/elec/SoCtMbCtbDP/Shr of Costs that Must be Covered to be Deemed Profitable.xlsx
+++ b/InputData/elec/SoCtMbCtbDP/Shr of Costs that Must be Covered to be Deemed Profitable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\elec\SoCtMbCtbDP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mary Francis Swint\Vensim\eps-indonesia\InputData\elec\SoCtMbCtbDP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87CF41B4-27AD-42C6-B841-9FDDA9AD063A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DFE90BD-22AB-4FA4-8F18-5A3209EFD48F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{5E78EF81-321F-43F5-B343-4E83A6575A8A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{5E78EF81-321F-43F5-B343-4E83A6575A8A}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -494,14 +494,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31DA106A-E484-4E2B-B3F9-91B326CF3E2A}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -520,12 +520,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.5703125" customWidth="1"/>
+    <col min="1" max="1" width="34.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>25</v>
       </c>
@@ -533,196 +533,196 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
       <c r="B4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
       <c r="B6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>9</v>
       </c>
       <c r="B8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>10</v>
       </c>
       <c r="B9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>11</v>
       </c>
       <c r="B10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>14</v>
       </c>
       <c r="B13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>15</v>
       </c>
       <c r="B14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>16</v>
       </c>
       <c r="B15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>17</v>
       </c>
       <c r="B16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>18</v>
       </c>
       <c r="B17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>19</v>
       </c>
       <c r="B18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>20</v>
       </c>
       <c r="B19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>21</v>
       </c>
       <c r="B20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>22</v>
       </c>
       <c r="B21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>23</v>
       </c>
       <c r="B22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>24</v>
       </c>
       <c r="B23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>27</v>
       </c>
       <c r="B24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>28</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>0.95</v>
       </c>
     </row>
   </sheetData>
@@ -731,6 +731,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002041A8AB53924247A2770D65450F5227" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="90fff4f083191fe75a03dbd50c7739fc">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1659011e-6b88-4225-9a61-aaf33aaf19e8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7fee88694a371868130ae0617c69143c" ns2:_="">
     <xsd:import namespace="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
@@ -874,15 +883,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -890,13 +890,36 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C6A9D6C-BB6D-4D60-817B-14ECC930D41F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55178A6E-2103-4547-883C-17AB31394776}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55178A6E-2103-4547-883C-17AB31394776}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C6A9D6C-BB6D-4D60-817B-14ECC930D41F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1659011e-6b88-4225-9a61-aaf33aaf19e8"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{935CF4FB-35E5-4196-A80B-AA5C5882639D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{935CF4FB-35E5-4196-A80B-AA5C5882639D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>